--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F806"/>
+  <dimension ref="A1:F836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21378,6 +21378,786 @@
         </is>
       </c>
     </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B807" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D807" t="n">
+        <v>849</v>
+      </c>
+      <c r="E807" t="n">
+        <v>899</v>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B808" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D808" t="n">
+        <v>849</v>
+      </c>
+      <c r="E808" t="n">
+        <v>899</v>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B809" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D809" t="n">
+        <v>849</v>
+      </c>
+      <c r="E809" t="n">
+        <v>899</v>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B810" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D810" t="n">
+        <v>749</v>
+      </c>
+      <c r="E810" t="n">
+        <v>799</v>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B811" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D811" t="n">
+        <v>499</v>
+      </c>
+      <c r="E811" t="n">
+        <v>549</v>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B812" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D812" t="n">
+        <v>799</v>
+      </c>
+      <c r="E812" t="n">
+        <v>899</v>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B813" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D813" t="n">
+        <v>549</v>
+      </c>
+      <c r="E813" t="n">
+        <v>649</v>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B814" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D814" t="n">
+        <v>749</v>
+      </c>
+      <c r="E814" t="n">
+        <v>799</v>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B815" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D815" t="n">
+        <v>499</v>
+      </c>
+      <c r="E815" t="n">
+        <v>549</v>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B816" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D816" t="n">
+        <v>469</v>
+      </c>
+      <c r="E816" t="n">
+        <v>499</v>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B817" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D817" t="n">
+        <v>649</v>
+      </c>
+      <c r="E817" t="n">
+        <v>699</v>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B818" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D818" t="n">
+        <v>749</v>
+      </c>
+      <c r="E818" t="n">
+        <v>799</v>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B819" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D819" t="n">
+        <v>799</v>
+      </c>
+      <c r="E819" t="n">
+        <v>899</v>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B820" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D820" t="n">
+        <v>549</v>
+      </c>
+      <c r="E820" t="n">
+        <v>649</v>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B821" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D821" t="n">
+        <v>599</v>
+      </c>
+      <c r="E821" t="n">
+        <v>649</v>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B822" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D822" t="n">
+        <v>568</v>
+      </c>
+      <c r="E822" t="n">
+        <v>549</v>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B823" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D823" t="n">
+        <v>649</v>
+      </c>
+      <c r="E823" t="n">
+        <v>699</v>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B824" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D824" t="n">
+        <v>597</v>
+      </c>
+      <c r="E824" t="n">
+        <v>649</v>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B825" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D825" t="n">
+        <v>599</v>
+      </c>
+      <c r="E825" t="n">
+        <v>649</v>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B826" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D826" t="n">
+        <v>599</v>
+      </c>
+      <c r="E826" t="n">
+        <v>649</v>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B827" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D827" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E827" t="n">
+        <v>999</v>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B828" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D828" t="n">
+        <v>649</v>
+      </c>
+      <c r="E828" t="n">
+        <v>699</v>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B829" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D829" t="n">
+        <v>549</v>
+      </c>
+      <c r="E829" t="n">
+        <v>649</v>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B830" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D830" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E830" t="n">
+        <v>899</v>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B831" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D831" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E831" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B832" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D832" t="n">
+        <v>799</v>
+      </c>
+      <c r="E832" t="n">
+        <v>899</v>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B833" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D833" t="n">
+        <v>649</v>
+      </c>
+      <c r="E833" t="n">
+        <v>699</v>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B834" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D834" t="n">
+        <v>499</v>
+      </c>
+      <c r="E834" t="n">
+        <v>649</v>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B835" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D835" t="n">
+        <v>598</v>
+      </c>
+      <c r="E835" t="n">
+        <v>649</v>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B836" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D836" t="n">
+        <v>599</v>
+      </c>
+      <c r="E836" t="n">
+        <v>399</v>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F836"/>
+  <dimension ref="A1:F866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22158,6 +22158,786 @@
         </is>
       </c>
     </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B837" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D837" t="n">
+        <v>849</v>
+      </c>
+      <c r="E837" t="n">
+        <v>899</v>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B838" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D838" t="n">
+        <v>849</v>
+      </c>
+      <c r="E838" t="n">
+        <v>899</v>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B839" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D839" t="n">
+        <v>849</v>
+      </c>
+      <c r="E839" t="n">
+        <v>899</v>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B840" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D840" t="n">
+        <v>749</v>
+      </c>
+      <c r="E840" t="n">
+        <v>799</v>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B841" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D841" t="n">
+        <v>499</v>
+      </c>
+      <c r="E841" t="n">
+        <v>549</v>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B842" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D842" t="n">
+        <v>799</v>
+      </c>
+      <c r="E842" t="n">
+        <v>899</v>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B843" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D843" t="n">
+        <v>549</v>
+      </c>
+      <c r="E843" t="n">
+        <v>649</v>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B844" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D844" t="n">
+        <v>749</v>
+      </c>
+      <c r="E844" t="n">
+        <v>799</v>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B845" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D845" t="n">
+        <v>499</v>
+      </c>
+      <c r="E845" t="n">
+        <v>549</v>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B846" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D846" t="n">
+        <v>469</v>
+      </c>
+      <c r="E846" t="n">
+        <v>499</v>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B847" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D847" t="n">
+        <v>649</v>
+      </c>
+      <c r="E847" t="n">
+        <v>699</v>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B848" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D848" t="n">
+        <v>749</v>
+      </c>
+      <c r="E848" t="n">
+        <v>799</v>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B849" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D849" t="n">
+        <v>799</v>
+      </c>
+      <c r="E849" t="n">
+        <v>899</v>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B850" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D850" t="n">
+        <v>549</v>
+      </c>
+      <c r="E850" t="n">
+        <v>649</v>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B851" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D851" t="n">
+        <v>599</v>
+      </c>
+      <c r="E851" t="n">
+        <v>649</v>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B852" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D852" t="n">
+        <v>568</v>
+      </c>
+      <c r="E852" t="n">
+        <v>549</v>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B853" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D853" t="n">
+        <v>649</v>
+      </c>
+      <c r="E853" t="n">
+        <v>699</v>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B854" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D854" t="n">
+        <v>597</v>
+      </c>
+      <c r="E854" t="n">
+        <v>649</v>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B855" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D855" t="n">
+        <v>599</v>
+      </c>
+      <c r="E855" t="n">
+        <v>649</v>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B856" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D856" t="n">
+        <v>599</v>
+      </c>
+      <c r="E856" t="n">
+        <v>649</v>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B857" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D857" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E857" t="n">
+        <v>999</v>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B858" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D858" t="n">
+        <v>649</v>
+      </c>
+      <c r="E858" t="n">
+        <v>699</v>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B859" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D859" t="n">
+        <v>549</v>
+      </c>
+      <c r="E859" t="n">
+        <v>649</v>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B860" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D860" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E860" t="n">
+        <v>899</v>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B861" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D861" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E861" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B862" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D862" t="n">
+        <v>799</v>
+      </c>
+      <c r="E862" t="n">
+        <v>899</v>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B863" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D863" t="n">
+        <v>649</v>
+      </c>
+      <c r="E863" t="n">
+        <v>699</v>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B864" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D864" t="n">
+        <v>499</v>
+      </c>
+      <c r="E864" t="n">
+        <v>649</v>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B865" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D865" t="n">
+        <v>598</v>
+      </c>
+      <c r="E865" t="n">
+        <v>649</v>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B866" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D866" t="n">
+        <v>599</v>
+      </c>
+      <c r="E866" t="n">
+        <v>399</v>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F866"/>
+  <dimension ref="A1:F896"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22938,6 +22938,786 @@
         </is>
       </c>
     </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B867" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D867" t="n">
+        <v>849</v>
+      </c>
+      <c r="E867" t="n">
+        <v>899</v>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B868" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D868" t="n">
+        <v>849</v>
+      </c>
+      <c r="E868" t="n">
+        <v>899</v>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B869" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D869" t="n">
+        <v>849</v>
+      </c>
+      <c r="E869" t="n">
+        <v>899</v>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B870" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D870" t="n">
+        <v>749</v>
+      </c>
+      <c r="E870" t="n">
+        <v>799</v>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B871" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D871" t="n">
+        <v>499</v>
+      </c>
+      <c r="E871" t="n">
+        <v>549</v>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B872" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D872" t="n">
+        <v>799</v>
+      </c>
+      <c r="E872" t="n">
+        <v>899</v>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B873" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D873" t="n">
+        <v>549</v>
+      </c>
+      <c r="E873" t="n">
+        <v>649</v>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B874" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D874" t="n">
+        <v>749</v>
+      </c>
+      <c r="E874" t="n">
+        <v>799</v>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B875" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D875" t="n">
+        <v>499</v>
+      </c>
+      <c r="E875" t="n">
+        <v>549</v>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B876" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D876" t="n">
+        <v>469</v>
+      </c>
+      <c r="E876" t="n">
+        <v>499</v>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B877" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D877" t="n">
+        <v>649</v>
+      </c>
+      <c r="E877" t="n">
+        <v>699</v>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B878" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D878" t="n">
+        <v>749</v>
+      </c>
+      <c r="E878" t="n">
+        <v>799</v>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B879" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D879" t="n">
+        <v>799</v>
+      </c>
+      <c r="E879" t="n">
+        <v>899</v>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B880" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D880" t="n">
+        <v>549</v>
+      </c>
+      <c r="E880" t="n">
+        <v>649</v>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B881" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D881" t="n">
+        <v>599</v>
+      </c>
+      <c r="E881" t="n">
+        <v>649</v>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B882" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D882" t="n">
+        <v>568</v>
+      </c>
+      <c r="E882" t="n">
+        <v>549</v>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B883" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D883" t="n">
+        <v>649</v>
+      </c>
+      <c r="E883" t="n">
+        <v>699</v>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B884" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D884" t="n">
+        <v>597</v>
+      </c>
+      <c r="E884" t="n">
+        <v>649</v>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B885" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D885" t="n">
+        <v>599</v>
+      </c>
+      <c r="E885" t="n">
+        <v>649</v>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B886" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D886" t="n">
+        <v>599</v>
+      </c>
+      <c r="E886" t="n">
+        <v>649</v>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B887" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D887" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E887" t="n">
+        <v>999</v>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B888" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D888" t="n">
+        <v>649</v>
+      </c>
+      <c r="E888" t="n">
+        <v>699</v>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B889" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D889" t="n">
+        <v>549</v>
+      </c>
+      <c r="E889" t="n">
+        <v>649</v>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B890" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D890" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E890" t="n">
+        <v>899</v>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B891" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D891" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E891" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B892" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D892" t="n">
+        <v>799</v>
+      </c>
+      <c r="E892" t="n">
+        <v>899</v>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B893" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D893" t="n">
+        <v>649</v>
+      </c>
+      <c r="E893" t="n">
+        <v>699</v>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B894" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D894" t="n">
+        <v>499</v>
+      </c>
+      <c r="E894" t="n">
+        <v>649</v>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B895" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D895" t="n">
+        <v>598</v>
+      </c>
+      <c r="E895" t="n">
+        <v>649</v>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B896" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D896" t="n">
+        <v>599</v>
+      </c>
+      <c r="E896" t="n">
+        <v>399</v>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F896"/>
+  <dimension ref="A1:F925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23718,6 +23718,760 @@
         </is>
       </c>
     </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B897" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D897" t="n">
+        <v>849</v>
+      </c>
+      <c r="E897" t="n">
+        <v>899</v>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B898" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D898" t="n">
+        <v>849</v>
+      </c>
+      <c r="E898" t="n">
+        <v>899</v>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B899" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D899" t="n">
+        <v>749</v>
+      </c>
+      <c r="E899" t="n">
+        <v>799</v>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B900" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D900" t="n">
+        <v>499</v>
+      </c>
+      <c r="E900" t="n">
+        <v>549</v>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B901" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D901" t="n">
+        <v>799</v>
+      </c>
+      <c r="E901" t="n">
+        <v>899</v>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B902" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D902" t="n">
+        <v>549</v>
+      </c>
+      <c r="E902" t="n">
+        <v>649</v>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B903" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D903" t="n">
+        <v>749</v>
+      </c>
+      <c r="E903" t="n">
+        <v>799</v>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B904" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D904" t="n">
+        <v>499</v>
+      </c>
+      <c r="E904" t="n">
+        <v>549</v>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B905" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D905" t="n">
+        <v>469</v>
+      </c>
+      <c r="E905" t="n">
+        <v>499</v>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B906" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D906" t="n">
+        <v>649</v>
+      </c>
+      <c r="E906" t="n">
+        <v>699</v>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B907" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D907" t="n">
+        <v>749</v>
+      </c>
+      <c r="E907" t="n">
+        <v>799</v>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B908" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D908" t="n">
+        <v>799</v>
+      </c>
+      <c r="E908" t="n">
+        <v>899</v>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B909" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D909" t="n">
+        <v>549</v>
+      </c>
+      <c r="E909" t="n">
+        <v>649</v>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B910" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D910" t="n">
+        <v>599</v>
+      </c>
+      <c r="E910" t="n">
+        <v>699</v>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B911" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D911" t="n">
+        <v>568</v>
+      </c>
+      <c r="E911" t="n">
+        <v>549</v>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B912" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D912" t="n">
+        <v>649</v>
+      </c>
+      <c r="E912" t="n">
+        <v>599</v>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B913" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D913" t="n">
+        <v>597</v>
+      </c>
+      <c r="E913" t="n">
+        <v>649</v>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B914" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D914" t="n">
+        <v>599</v>
+      </c>
+      <c r="E914" t="n">
+        <v>649</v>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B915" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D915" t="n">
+        <v>599</v>
+      </c>
+      <c r="E915" t="n">
+        <v>649</v>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B916" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D916" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E916" t="n">
+        <v>999</v>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B917" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D917" t="n">
+        <v>649</v>
+      </c>
+      <c r="E917" t="n">
+        <v>699</v>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B918" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D918" t="n">
+        <v>549</v>
+      </c>
+      <c r="E918" t="n">
+        <v>699</v>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B919" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D919" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E919" t="n">
+        <v>899</v>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B920" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D920" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E920" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B921" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D921" t="n">
+        <v>799</v>
+      </c>
+      <c r="E921" t="n">
+        <v>899</v>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B922" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D922" t="n">
+        <v>649</v>
+      </c>
+      <c r="E922" t="n">
+        <v>699</v>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B923" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D923" t="n">
+        <v>499</v>
+      </c>
+      <c r="E923" t="n">
+        <v>649</v>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B924" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D924" t="n">
+        <v>598</v>
+      </c>
+      <c r="E924" t="n">
+        <v>649</v>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B925" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D925" t="n">
+        <v>599</v>
+      </c>
+      <c r="E925" t="n">
+        <v>399</v>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F925"/>
+  <dimension ref="A1:F955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24472,6 +24472,786 @@
         </is>
       </c>
     </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B926" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D926" t="n">
+        <v>849</v>
+      </c>
+      <c r="E926" t="n">
+        <v>899</v>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B927" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D927" t="n">
+        <v>849</v>
+      </c>
+      <c r="E927" t="n">
+        <v>899</v>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B928" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D928" t="n">
+        <v>749</v>
+      </c>
+      <c r="E928" t="n">
+        <v>799</v>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B929" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D929" t="n">
+        <v>499</v>
+      </c>
+      <c r="E929" t="n">
+        <v>549</v>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B930" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D930" t="n">
+        <v>799</v>
+      </c>
+      <c r="E930" t="n">
+        <v>899</v>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B931" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D931" t="n">
+        <v>549</v>
+      </c>
+      <c r="E931" t="n">
+        <v>649</v>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B932" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D932" t="n">
+        <v>749</v>
+      </c>
+      <c r="E932" t="n">
+        <v>799</v>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B933" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D933" t="n">
+        <v>499</v>
+      </c>
+      <c r="E933" t="n">
+        <v>549</v>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B934" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D934" t="n">
+        <v>469</v>
+      </c>
+      <c r="E934" t="n">
+        <v>499</v>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B935" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D935" t="n">
+        <v>649</v>
+      </c>
+      <c r="E935" t="n">
+        <v>699</v>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B936" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D936" t="n">
+        <v>749</v>
+      </c>
+      <c r="E936" t="n">
+        <v>799</v>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B937" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D937" t="n">
+        <v>799</v>
+      </c>
+      <c r="E937" t="n">
+        <v>899</v>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B938" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D938" t="n">
+        <v>549</v>
+      </c>
+      <c r="E938" t="n">
+        <v>649</v>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B939" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D939" t="n">
+        <v>599</v>
+      </c>
+      <c r="E939" t="n">
+        <v>699</v>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B940" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D940" t="n">
+        <v>568</v>
+      </c>
+      <c r="E940" t="n">
+        <v>549</v>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B941" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D941" t="n">
+        <v>649</v>
+      </c>
+      <c r="E941" t="n">
+        <v>599</v>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B942" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D942" t="n">
+        <v>597</v>
+      </c>
+      <c r="E942" t="n">
+        <v>649</v>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B943" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D943" t="n">
+        <v>599</v>
+      </c>
+      <c r="E943" t="n">
+        <v>649</v>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B944" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D944" t="n">
+        <v>599</v>
+      </c>
+      <c r="E944" t="n">
+        <v>649</v>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B945" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D945" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E945" t="n">
+        <v>999</v>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B946" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D946" t="n">
+        <v>649</v>
+      </c>
+      <c r="E946" t="n">
+        <v>599</v>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B947" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D947" t="n">
+        <v>549</v>
+      </c>
+      <c r="E947" t="n">
+        <v>699</v>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B948" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D948" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E948" t="n">
+        <v>899</v>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B949" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D949" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E949" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B950" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D950" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E950" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B951" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D951" t="n">
+        <v>799</v>
+      </c>
+      <c r="E951" t="n">
+        <v>899</v>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B952" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D952" t="n">
+        <v>649</v>
+      </c>
+      <c r="E952" t="n">
+        <v>599</v>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B953" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D953" t="n">
+        <v>499</v>
+      </c>
+      <c r="E953" t="n">
+        <v>649</v>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B954" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D954" t="n">
+        <v>598</v>
+      </c>
+      <c r="E954" t="n">
+        <v>649</v>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B955" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D955" t="n">
+        <v>599</v>
+      </c>
+      <c r="E955" t="n">
+        <v>399</v>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F955"/>
+  <dimension ref="A1:F986"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25252,6 +25252,812 @@
         </is>
       </c>
     </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B956" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D956" t="n">
+        <v>849</v>
+      </c>
+      <c r="E956" t="n">
+        <v>899</v>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B957" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D957" t="n">
+        <v>849</v>
+      </c>
+      <c r="E957" t="n">
+        <v>899</v>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D958" t="n">
+        <v>849</v>
+      </c>
+      <c r="E958" t="n">
+        <v>899</v>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D959" t="n">
+        <v>749</v>
+      </c>
+      <c r="E959" t="n">
+        <v>699</v>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D960" t="n">
+        <v>499</v>
+      </c>
+      <c r="E960" t="n">
+        <v>549</v>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D961" t="n">
+        <v>799</v>
+      </c>
+      <c r="E961" t="n">
+        <v>899</v>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D962" t="n">
+        <v>549</v>
+      </c>
+      <c r="E962" t="n">
+        <v>649</v>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B963" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D963" t="n">
+        <v>749</v>
+      </c>
+      <c r="E963" t="n">
+        <v>699</v>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D964" t="n">
+        <v>499</v>
+      </c>
+      <c r="E964" t="n">
+        <v>549</v>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B965" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D965" t="n">
+        <v>469</v>
+      </c>
+      <c r="E965" t="n">
+        <v>499</v>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D966" t="n">
+        <v>649</v>
+      </c>
+      <c r="E966" t="n">
+        <v>697</v>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D967" t="n">
+        <v>749</v>
+      </c>
+      <c r="E967" t="n">
+        <v>699</v>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B968" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D968" t="n">
+        <v>799</v>
+      </c>
+      <c r="E968" t="n">
+        <v>899</v>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D969" t="n">
+        <v>549</v>
+      </c>
+      <c r="E969" t="n">
+        <v>649</v>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B970" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D970" t="n">
+        <v>599</v>
+      </c>
+      <c r="E970" t="n">
+        <v>699</v>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B971" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D971" t="n">
+        <v>568</v>
+      </c>
+      <c r="E971" t="n">
+        <v>549</v>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B972" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D972" t="n">
+        <v>649</v>
+      </c>
+      <c r="E972" t="n">
+        <v>599</v>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D973" t="n">
+        <v>597</v>
+      </c>
+      <c r="E973" t="n">
+        <v>649</v>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D974" t="n">
+        <v>599</v>
+      </c>
+      <c r="E974" t="n">
+        <v>649</v>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D975" t="n">
+        <v>599</v>
+      </c>
+      <c r="E975" t="n">
+        <v>649</v>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D976" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E976" t="n">
+        <v>999</v>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B977" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D977" t="n">
+        <v>649</v>
+      </c>
+      <c r="E977" t="n">
+        <v>599</v>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B978" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D978" t="n">
+        <v>549</v>
+      </c>
+      <c r="E978" t="n">
+        <v>699</v>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B979" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D979" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E979" t="n">
+        <v>799</v>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B980" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D980" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E980" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B981" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D981" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E981" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B982" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D982" t="n">
+        <v>799</v>
+      </c>
+      <c r="E982" t="n">
+        <v>899</v>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B983" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D983" t="n">
+        <v>649</v>
+      </c>
+      <c r="E983" t="n">
+        <v>599</v>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B984" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D984" t="n">
+        <v>499</v>
+      </c>
+      <c r="E984" t="n">
+        <v>649</v>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B985" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D985" t="n">
+        <v>598</v>
+      </c>
+      <c r="E985" t="n">
+        <v>649</v>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B986" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D986" t="n">
+        <v>599</v>
+      </c>
+      <c r="E986" t="n">
+        <v>399</v>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F986"/>
+  <dimension ref="A1:F1014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26058,6 +26058,734 @@
         </is>
       </c>
     </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B987" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D987" t="n">
+        <v>849</v>
+      </c>
+      <c r="E987" t="n">
+        <v>899</v>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B988" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D988" t="n">
+        <v>749</v>
+      </c>
+      <c r="E988" t="n">
+        <v>699</v>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B989" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D989" t="n">
+        <v>499</v>
+      </c>
+      <c r="E989" t="n">
+        <v>549</v>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B990" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D990" t="n">
+        <v>799</v>
+      </c>
+      <c r="E990" t="n">
+        <v>899</v>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B991" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D991" t="n">
+        <v>549</v>
+      </c>
+      <c r="E991" t="n">
+        <v>649</v>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B992" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D992" t="n">
+        <v>749</v>
+      </c>
+      <c r="E992" t="n">
+        <v>699</v>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B993" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D993" t="n">
+        <v>499</v>
+      </c>
+      <c r="E993" t="n">
+        <v>549</v>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B994" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D994" t="n">
+        <v>469</v>
+      </c>
+      <c r="E994" t="n">
+        <v>499</v>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B995" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D995" t="n">
+        <v>649</v>
+      </c>
+      <c r="E995" t="n">
+        <v>697</v>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B996" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D996" t="n">
+        <v>749</v>
+      </c>
+      <c r="E996" t="n">
+        <v>699</v>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B997" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D997" t="n">
+        <v>799</v>
+      </c>
+      <c r="E997" t="n">
+        <v>899</v>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B998" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D998" t="n">
+        <v>549</v>
+      </c>
+      <c r="E998" t="n">
+        <v>649</v>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B999" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D999" t="n">
+        <v>599</v>
+      </c>
+      <c r="E999" t="n">
+        <v>699</v>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1000" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1000" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1001" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1001" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1002" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1002" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1003" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1003" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1004" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1004" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1005" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1005" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1006" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1006" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1007" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1007" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1008" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1008" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1009" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1009" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1010" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1010" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>898</v>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1011" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1011" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1012" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1012" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1013" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1013" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1014" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1014" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1014"/>
+  <dimension ref="A1:F1044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26786,6 +26786,786 @@
         </is>
       </c>
     </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B1015" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D1015" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B1016" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1016" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B1017" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D1017" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1018" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1018" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1019" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1019" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1020" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1020" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1021" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1021" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1022" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1022" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1023" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1023" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1024" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1024" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1025" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1025" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1026" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1026" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1027" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1027" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1028" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1028" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1029" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1029" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1030" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1030" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1031" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1031" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1032" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1032" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1033" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1033" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1034" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1034" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1035" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1035" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1036" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1036" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1037" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1037" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1038" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1038" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1039" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1039" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1040" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1040" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1041" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1041" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1042" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1042" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1042" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1043" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1043" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1044" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1044" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1044"/>
+  <dimension ref="A1:F1074"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27566,6 +27566,786 @@
         </is>
       </c>
     </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B1045" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D1045" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B1046" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1046" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B1047" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D1047" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1047" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1048" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1048" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1048" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1049" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1049" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1049" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1050" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1050" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1050" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1051" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1051" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1052" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1052" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1052" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1053" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1053" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1054" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1054" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1054" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1055" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1055" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1055" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1056" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1056" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1057" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1057" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1057" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1058" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1058" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1059" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1059" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1060" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1060" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1061" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1061" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1062" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1062" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1063" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1063" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1064" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1064" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1065" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1065" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1066" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1066" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1067" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1067" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1068" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1068" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1069" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1069" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1070" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1070" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1071" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1071" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1072" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1072" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1073" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1073" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1074" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1074" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1074"/>
+  <dimension ref="A1:F1102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28346,6 +28346,734 @@
         </is>
       </c>
     </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B1075" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D1075" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1076" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1076" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1077" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1077" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1078" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1078" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1079" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1079" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1080" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1080" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1081" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1081" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1082" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1082" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1083" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1084" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1085" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1085" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1086" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1086" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1087" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1087" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1088" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1088" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1089" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1089" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1090" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1091" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1091" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1092" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1092" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1093" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1093" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1094" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1094" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1095" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1095" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1096" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1096" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1097" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1097" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1098" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1098" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1099" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1099" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1100" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1100" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1101" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1101" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1102" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1102" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1102"/>
+  <dimension ref="A1:F1128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29074,6 +29074,682 @@
         </is>
       </c>
     </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1103" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1103" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1104" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1104" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1105" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1105" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1106" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1106" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1107" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1107" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1108" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1108" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1109" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1109" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1110" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1110" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1111" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1111" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1112" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1112" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1113" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1113" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1114" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1114" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1115" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1115" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1116" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1116" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1117" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1117" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1118" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1118" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1119" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1119" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1120" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1120" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1121" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1121" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1122" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1122" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1123" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1123" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1124" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1124" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1125" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1125" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1126" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1126" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1127" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1127" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1128" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1128" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1128"/>
+  <dimension ref="A1:F1159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29750,6 +29750,812 @@
         </is>
       </c>
     </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B1129" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D1129" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B1130" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1130" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B1131" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D1131" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1132" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1132" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1133" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1133" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1134" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1134" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1135" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1135" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1136" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1136" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1137" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1137" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1138" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1138" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1139" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1139" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1140" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1140" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1141" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1141" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1142" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1142" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1143" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1143" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1144" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1144" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1145" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1145" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1146" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1146" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1147" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1147" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1148" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1148" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1149" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1149" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1150" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1150" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1151" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1151" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1152" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1152" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1153" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1153" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1154" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1154" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1155" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1155" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1156" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1156" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1157" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1157" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1158" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1158" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1159" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1159" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1159"/>
+  <dimension ref="A1:F1189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30556,6 +30556,786 @@
         </is>
       </c>
     </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B1160" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D1160" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B1161" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1161" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B1162" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D1162" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1163" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1163" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1164" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1164" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1165" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1165" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1166" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1166" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1167" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1167" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1168" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1168" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1169" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1169" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1169" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1170" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1170" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1171" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1171" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1172" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1172" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1173" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1173" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1174" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1174" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1175" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1175" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1176" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1176" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1177" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1177" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1178" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1178" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1179" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1179" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1180" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1180" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1181" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1181" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1182" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1182" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1183" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1183" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1184" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1184" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1185" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1185" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>898</v>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1186" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1186" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1187" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1187" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1188" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1188" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1189" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1189" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1189"/>
+  <dimension ref="A1:F1219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31336,6 +31336,786 @@
         </is>
       </c>
     </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B1190" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D1190" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B1191" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1191" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B1192" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D1192" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1193" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1193" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1194" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1194" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1195" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1195" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1196" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1196" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1197" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1197" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1198" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1198" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1199" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1199" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1200" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1200" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1201" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1201" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1202" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1202" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1203" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1203" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1204" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1204" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1205" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1205" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1206" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1206" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1207" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1207" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1208" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1208" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1209" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1209" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1210" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1210" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1211" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1211" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1212" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1212" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1213" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1213" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1214" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1214" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1215" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1215" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1216" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1216" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1217" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1217" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1218" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1218" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1219" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1219" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1219"/>
+  <dimension ref="A1:F1249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32116,6 +32116,786 @@
         </is>
       </c>
     </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B1220" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D1220" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B1221" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1221" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B1222" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D1222" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1223" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1223" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1224" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1224" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1225" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1225" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1226" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1226" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1227" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1227" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1228" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1228" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1229" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1229" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1230" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1230" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1231" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1231" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1232" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1232" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1233" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1233" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1234" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1234" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1235" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1235" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1236" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1236" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1237" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1237" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1238" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1238" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1239" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1239" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1240" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1240" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1241" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1241" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1242" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1242" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1243" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1243" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1244" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1244" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1245" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1245" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1246" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1246" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1247" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1247" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1248" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1248" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1249" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1249" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1249"/>
+  <dimension ref="A1:F1276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32896,6 +32896,708 @@
         </is>
       </c>
     </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1250" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1250" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1251" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1251" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1252" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1252" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1253" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1253" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1254" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1254" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1255" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1255" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1256" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1256" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1257" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1257" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1258" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1258" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1259" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1259" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1260" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1260" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1261" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1261" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1262" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1262" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1263" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1263" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1263" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1264" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1264" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1264" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1265" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1265" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1266" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1266" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1266" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1267" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1267" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1267" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1268" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1268" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1268" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1269" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1269" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1269" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1270" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1270" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1270" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1271" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1271" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1271" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1272" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1272" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1272" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1273" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1273" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1273" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1274" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1274" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1274" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1275" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1275" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1275" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1276" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1276" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1276" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1276"/>
+  <dimension ref="A1:F1304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33598,6 +33598,734 @@
         </is>
       </c>
     </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1277" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1277" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1277" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1278" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1278" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1278" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1279" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1279" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1279" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1280" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1280" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1280" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1281" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1281" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1281" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1282" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1282" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1282" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1283" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1283" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1283" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1284" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1284" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1284" t="n">
+        <v>697</v>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1285" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1285" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1285" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1286" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1286" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1286" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1287" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1287" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1287" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1288" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1288" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1288" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1289" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1289" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1289" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1290" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1290" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1290" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1291" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1291" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1291" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1292" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1292" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1292" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1293" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1293" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1293" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1294" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1294" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1294" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1295" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1295" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1295" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1296" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1296" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1296" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1297" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1297" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1297" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1298" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1298" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1298" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1299" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1299" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1299" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1300" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1300" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1300" t="n">
+        <v>898</v>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1301" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1301" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1301" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1302" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1302" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1303" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1303" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1303" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1304" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1304" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1304" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1304"/>
+  <dimension ref="A1:F1331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34326,6 +34326,708 @@
         </is>
       </c>
     </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1305" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1305" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1305" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1306" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1306" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1306" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1307" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1307" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1308" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1308" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1309" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1309" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1309" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1310" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1310" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1311" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1311" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1311" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1312" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1312" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1312" t="n">
+        <v>697</v>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1313" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1313" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1314" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1314" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1314" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1315" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1315" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1315" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1316" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1316" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1316" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1317" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1317" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1318" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1318" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1319" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1319" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1320" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1320" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1321" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1321" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1322" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1322" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1322" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1323" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1323" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1324" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1324" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1325" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1325" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1326" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1326" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1327" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1327" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>898</v>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1328" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1328" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1329" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1329" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1330" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1330" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1331" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1331" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1331"/>
+  <dimension ref="A1:F1358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35028,6 +35028,708 @@
         </is>
       </c>
     </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1332" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1332" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1333" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1333" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1334" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1334" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1335" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1335" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1336" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1336" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1337" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1337" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1338" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1338" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1339" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1339" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1340" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1340" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1341" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1341" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1341" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1342" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1342" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1343" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1343" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1343" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1344" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1344" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1344" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1345" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1345" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1345" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1346" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1346" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1346" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1347" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1347" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1347" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1348" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1348" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1348" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1349" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1349" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1350" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1350" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1351" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1351" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1352" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1352" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1353" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1353" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1354" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1354" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>898</v>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1355" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1355" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1355" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1356" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1356" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1357" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1357" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1358" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1358" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1358"/>
+  <dimension ref="A1:F1385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35730,6 +35730,708 @@
         </is>
       </c>
     </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1359" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1359" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1360" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1360" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1361" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1361" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1362" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1362" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1363" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1363" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1364" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1364" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1365" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1365" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1366" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1366" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1367" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1367" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1368" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1368" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1369" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1369" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1370" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1370" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1371" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1371" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1372" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1372" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1373" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1373" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1374" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1374" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1375" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1375" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1376" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1376" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1377" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1377" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1378" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1378" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1379" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1379" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1380" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1380" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1380" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1381" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1381" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1381" t="n">
+        <v>898</v>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1382" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1382" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1382" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1383" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1383" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1384" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1384" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1385" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1385" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1385" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1385"/>
+  <dimension ref="A1:F1412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36432,6 +36432,708 @@
         </is>
       </c>
     </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1386" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1386" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1386" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1387" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1387" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1387" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1388" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1388" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1389" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1389" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1390" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1390" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1391" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1391" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1391" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1392" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1392" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1393" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1393" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1393" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1394" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1394" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1394" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1395" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1395" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1395" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1396" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1396" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1396" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1397" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1397" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1397" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1398" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1398" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1398" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1399" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1399" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1399" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1400" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1400" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1400" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1401" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1401" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1401" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1402" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1402" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1402" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1403" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1403" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1403" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1404" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1404" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1404" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1405" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1405" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1405" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1406" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1406" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1406" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1407" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1407" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1407" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1408" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1408" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1408" t="n">
+        <v>898</v>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1409" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1409" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1409" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1410" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1410" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1410" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1411" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1411" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1411" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1412" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1412" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1412" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1412"/>
+  <dimension ref="A1:F1439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37134,6 +37134,708 @@
         </is>
       </c>
     </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1413" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1413" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1413" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1414" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1414" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1414" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1415" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1415" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1415" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1416" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1416" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1416" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1417" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1417" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1417" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1418" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1418" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1418" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1419" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1419" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1419" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1420" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1420" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1420" t="n">
+        <v>697</v>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1421" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1421" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1422" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1422" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1422" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1423" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1423" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1423" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1424" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1424" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1424" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1425" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1425" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1425" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1426" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1426" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1426" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1427" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1427" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1427" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1428" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1428" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1428" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1429" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1429" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1429" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1430" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1430" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1430" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1431" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1431" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1431" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1432" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1432" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1432" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1433" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1433" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1433" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1434" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1434" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1435" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1435" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>898</v>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1436" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1436" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1436" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1437" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1437" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1437" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1438" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1438" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1438" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1439" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1439" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1439" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1439"/>
+  <dimension ref="A1:F1467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37836,6 +37836,734 @@
         </is>
       </c>
     </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1440" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1440" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1440" t="n">
+        <v>797</v>
+      </c>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1441" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1441" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1441" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1442" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1442" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1442" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1443" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1443" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1443" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1444" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1444" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1444" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1445" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1445" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1445" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1446" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1446" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1446" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1447" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1447" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1447" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1448" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1448" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1448" t="n">
+        <v>797</v>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1449" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1449" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1450" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1450" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1451" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1451" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1452" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1452" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1453" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1453" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1453" t="n">
+        <v>697</v>
+      </c>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1454" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1454" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1454" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1455" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1455" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1455" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1455" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1456" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1456" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1456" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1457" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1457" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1458" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1458" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1458" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1459" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1459" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1459" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1460" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1460" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1460" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1461" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1461" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1461" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1462" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1462" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1462" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1463" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1463" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>898</v>
+      </c>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1464" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1464" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1465" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1465" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1465" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1466" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1466" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1466" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1467" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1467" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1467" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1467"/>
+  <dimension ref="A1:F1495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38564,6 +38564,734 @@
         </is>
       </c>
     </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>ACCHH5CANBAJRJ5N</t>
+        </is>
+      </c>
+      <c r="B1468" t="n">
+        <v>140319834</v>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1468" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1469" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1469" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>ACCHGBHAF6EXRYE4</t>
+        </is>
+      </c>
+      <c r="B1470" t="n">
+        <v>140319831</v>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1470" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1471" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1471" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>ACCHGBHAGCMKDTYF</t>
+        </is>
+      </c>
+      <c r="B1472" t="n">
+        <v>140319835</v>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro w/ 65hrs Playtime, AI-ENC Calls, Pristine Sound, Dual-device Pairing Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1472" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1473" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1473" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1474" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1474" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1475" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1475" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>ACCHGBHAD28ZGGPH</t>
+        </is>
+      </c>
+      <c r="B1476" t="n">
+        <v>140319836</v>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>PTron Studio Pro Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1476" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>799</v>
+      </c>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFGC8ANG9</t>
+        </is>
+      </c>
+      <c r="B1477" t="n">
+        <v>140319832</v>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1477" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1477" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1478" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1478" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1478" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>ACCHMH9QHVNJUGVH</t>
+        </is>
+      </c>
+      <c r="B1479" t="n">
+        <v>140319983</v>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Plum Perfect)</t>
+        </is>
+      </c>
+      <c r="D1479" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1479" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1480" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1480" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1480" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>ACCHH5CAHYCBHZCZ</t>
+        </is>
+      </c>
+      <c r="B1481" t="n">
+        <v>140319837</v>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth &amp; Wired  (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1481" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1481" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>ACCHHB69Z4WXBVZU</t>
+        </is>
+      </c>
+      <c r="B1482" t="n">
+        <v>140319875</v>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Black, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1482" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1482" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>ACCHG53YUXCJ5XMU</t>
+        </is>
+      </c>
+      <c r="B1483" t="n">
+        <v>140319888</v>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Gray)</t>
+        </is>
+      </c>
+      <c r="D1483" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1483" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1484" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1484" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1484" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1485" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1485" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>ACCHGBHASAMQNEVH</t>
+        </is>
+      </c>
+      <c r="B1486" t="n">
+        <v>140319838</v>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Blue, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1486" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1487" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1487" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1487" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1488" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1488" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1489" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1489" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1490" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1490" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>ACCHGBHAVXA6ESGG</t>
+        </is>
+      </c>
+      <c r="B1491" t="n">
+        <v>140319830</v>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>PTron Studio Classic w/ 75hrs Playtime, AI-ENC Calls, 40mm Driver, Dual-device Pairing Bluetooth  (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1491" t="n">
+        <v>799</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>898</v>
+      </c>
+      <c r="F1491" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>ACCHGBHAFCEAQGHZ</t>
+        </is>
+      </c>
+      <c r="B1492" t="n">
+        <v>140319839</v>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>PTron Studio w/ 60hrs Playtime, HD Mic, 40mm Drivers, Dual-device Pairing, BT5.4 Bluetooth  (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1492" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1493" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1493" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1493" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1494" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1494" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1494" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1495" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1495" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1495" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1495"/>
+  <dimension ref="A1:F1512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39292,6 +39292,445 @@
         </is>
       </c>
     </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1496" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1496" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1496" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1497" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1497" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1497" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1498" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1498" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1498" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1499" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1499" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1499" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1500" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1500" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1501" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1501" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1501" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1502" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1502" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1502" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1503" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1503" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1503" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1504" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1504" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1504" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1505" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1505" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1505" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1506" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1506" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1506" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1507" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1507" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1507" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1508" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1508" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1508" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1509" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1509" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1509" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1510" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1510" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1510" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1511" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1511" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1511" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1512" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1512" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1512" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1512"/>
+  <dimension ref="A1:F1530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39731,6 +39731,471 @@
         </is>
       </c>
     </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1513" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1513" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1513" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1514" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1514" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1514" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1515" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1515" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1515" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1515" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1516" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1516" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1516" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1517" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1517" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1517" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1518" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1518" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1519" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1519" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1519" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1520" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1520" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1520" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1521" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1521" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1521" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1522" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1522" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1522" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1522" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1523" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1523" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1523" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1523" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1524" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1524" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1524" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1525" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1525" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1525" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1525" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1526" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1526" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1526" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1526" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1527" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1527" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1527" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1527" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1528" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1528" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1528" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1528" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1529" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1529" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1529" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1529" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1530" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1530" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1530" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1530" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1530"/>
+  <dimension ref="A1:F1548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40196,6 +40196,471 @@
         </is>
       </c>
     </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1531" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1531" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1531" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1531" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1532" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1532" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1532" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1532" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1533" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1533" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1533" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1534" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1534" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1534" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1534" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1535" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1535" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1535" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1535" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1536" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1536" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1536" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1537" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1537" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1537" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1537" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1538" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1538" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1538" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1538" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1539" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1539" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1539" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1539" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1540" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1540" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1540" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1540" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1541" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1541" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1541" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1541" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1542" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1542" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1542" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1542" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1543" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1543" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1543" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1543" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1544" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1544" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1544" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1544" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1545" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1545" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1545" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1545" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1546" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1546" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1546" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1546" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1547" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1547" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1547" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1547" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1548" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1548" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1548" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1548" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1548"/>
+  <dimension ref="A1:F1565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40661,6 +40661,445 @@
         </is>
       </c>
     </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1549" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1549" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1549" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1549" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1550" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1550" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1550" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1550" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1551" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1551" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1551" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1551" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1552" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1552" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1552" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1552" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1553" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1553" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1553" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1554" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1554" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1554" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1554" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1555" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1555" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1555" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1555" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1556" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1556" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1556" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1557" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1557" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1557" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1557" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1558" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1558" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1558" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1558" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1559" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1559" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1559" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1559" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1560" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1560" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1560" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1560" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1561" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1561" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1561" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1561" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1562" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1562" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1562" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1562" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1563" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1563" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1563" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1563" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1564" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1564" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1564" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1564" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1565" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1565" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1565" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1565"/>
+  <dimension ref="A1:F1583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41100,6 +41100,471 @@
         </is>
       </c>
     </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1566" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1566" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1566" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1566" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1567" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1567" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1567" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1567" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1568" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1568" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1568" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1568" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1569" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1569" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1569" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1569" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1570" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1570" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1570" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1570" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1571" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1571" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1571" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1572" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1572" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1572" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1572" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1573" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1573" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1573" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1573" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1574" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1574" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1574" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1574" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1575" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1575" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1575" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1575" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1576" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1576" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1576" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1576" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1577" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1577" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1577" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1578" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1578" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1578" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1579" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1579" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1579" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1580" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1580" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1580" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1581" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1581" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1581" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1582" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1582" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1582" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1583" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1583" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1583" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1583"/>
+  <dimension ref="A1:F1601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41565,6 +41565,471 @@
         </is>
       </c>
     </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1584" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1584" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1584" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1585" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1585" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1585" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1586" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1586" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1586" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1586" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1587" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1587" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1587" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1588" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1588" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1588" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1588" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1589" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1589" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1589" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1590" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1590" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1590" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1590" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1591" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1591" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1591" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1591" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1592" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1592" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1592" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1592" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1593" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1593" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1593" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1593" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1594" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1594" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1594" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1594" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1595" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1595" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1595" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1595" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1596" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1596" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1596" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1596" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1597" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1597" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1597" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1597" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1598" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1598" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1598" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1598" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1599" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1599" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1599" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1599" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1600" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1600" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1600" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1600" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1601" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1601" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1601" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1601" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1601"/>
+  <dimension ref="A1:F1619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42030,6 +42030,471 @@
         </is>
       </c>
     </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1602" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1602" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1602" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1603" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1603" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1603" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1603" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1604" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1604" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1604" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1604" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1605" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1605" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1605" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1605" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>ACCHCYDFUSZB8FYG</t>
+        </is>
+      </c>
+      <c r="B1606" t="n">
+        <v>140319735</v>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Rogue TWS Earbuds (Black)</t>
+        </is>
+      </c>
+      <c r="D1606" t="n">
+        <v>649</v>
+      </c>
+      <c r="E1606" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1606" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1607" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1607" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1607" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1608" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1608" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1608" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1608" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1609" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1609" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1609" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1609" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1610" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1610" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1610" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1610" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1611" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1611" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1611" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1611" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1612" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1612" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1612" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1612" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1613" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1613" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1613" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1613" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1614" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1614" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1614" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1614" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1615" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1615" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1615" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1615" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1616" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1616" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1616" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1616" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1617" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1617" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1617" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1617" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1618" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1618" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1618" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1618" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1619" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1619" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1619" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1619" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1619"/>
+  <dimension ref="A1:F1636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42495,6 +42495,445 @@
         </is>
       </c>
     </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1620" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1620" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1620" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1620" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1621" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1621" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1621" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1621" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1622" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1622" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1622" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1622" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1623" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1623" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1623" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1623" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1624" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1624" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1624" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1625" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1625" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1625" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1625" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1626" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1626" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1626" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1626" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1627" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1627" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1627" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1627" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1628" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1628" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1628" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1628" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1629" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1629" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1629" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1629" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1630" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1630" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1630" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1630" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1631" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1631" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1631" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1631" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1632" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1632" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1632" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1632" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1633" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1633" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1633" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1633" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1634" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1634" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1634" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1634" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1635" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1635" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1635" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1635" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1636" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1636" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1636" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1636" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1636"/>
+  <dimension ref="A1:F1653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42934,6 +42934,445 @@
         </is>
       </c>
     </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1637" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1637" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1637" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1637" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1638" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1638" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1638" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1638" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1639" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1639" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1639" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1639" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1640" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1640" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1640" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1640" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1641" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1641" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1641" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1642" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1642" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1642" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1642" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1643" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1643" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1643" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1643" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1644" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1644" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1644" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1644" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1645" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1645" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1645" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1645" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1646" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1646" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1646" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1646" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1647" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1647" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1647" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1647" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1648" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1648" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1648" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1648" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1649" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1649" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1649" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1649" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1650" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1650" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1650" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1650" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1651" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1651" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1651" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1651" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1652" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1652" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1652" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1652" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1653" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1653" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1653" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1653" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1653"/>
+  <dimension ref="A1:F1670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43373,6 +43373,445 @@
         </is>
       </c>
     </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1654" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1654" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1654" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1654" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1655" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1655" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1655" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1655" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1656" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1656" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1656" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1656" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1657" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1657" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1657" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1657" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1658" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1658" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1658" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1659" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1659" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1659" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1659" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1660" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1660" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1660" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1660" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1661" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1661" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1661" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1661" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1662" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1662" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1662" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1662" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1663" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1663" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1663" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1663" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1664" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1664" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1664" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1664" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1665" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1665" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1665" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1665" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1666" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1666" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1666" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1666" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1667" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1667" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1667" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1667" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1668" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1668" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1668" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1668" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1669" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1669" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1669" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1669" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1670" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1670" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1670" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1670" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1670"/>
+  <dimension ref="A1:F1687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43812,6 +43812,445 @@
         </is>
       </c>
     </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1671" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1671" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1671" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1671" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1672" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1672" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1672" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1672" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1673" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1673" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1673" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1673" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1674" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1674" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1674" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1674" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1675" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1675" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1675" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1676" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1676" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1676" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1676" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1677" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1677" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1677" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1677" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1678" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1678" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1678" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1678" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1679" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1679" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1679" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1679" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1680" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1680" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1680" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1680" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1681" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1681" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1681" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1681" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1682" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1682" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1682" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1682" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1683" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1683" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1683" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1683" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1684" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1684" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1684" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1684" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1685" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1685" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1685" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1685" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1686" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1686" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1686" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1686" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1687" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1687" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1687" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1687" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1687"/>
+  <dimension ref="A1:F1704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44251,6 +44251,445 @@
         </is>
       </c>
     </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1688" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1688" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1688" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1688" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1689" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1689" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1689" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1689" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1690" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1690" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1690" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1690" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1691" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1691" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1691" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1691" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1692" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1692" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1692" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1693" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1693" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1693" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1693" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1694" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1694" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1694" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1694" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1695" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1695" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1695" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1695" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1696" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1696" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1696" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1696" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1697" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1697" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1697" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1697" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1698" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1698" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1698" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1698" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1699" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1699" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1699" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1699" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1700" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1700" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1700" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1700" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1701" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1701" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1701" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1701" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1702" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1702" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1702" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1702" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1703" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1703" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1703" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1703" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1704" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1704" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1704" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1704" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1704"/>
+  <dimension ref="A1:F1721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44690,6 +44690,445 @@
         </is>
       </c>
     </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1705" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1705" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1705" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1705" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1706" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1706" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1706" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1706" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1707" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1707" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1707" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1707" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1708" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1708" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1708" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1708" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1709" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1709" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1709" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1710" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1710" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1710" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1710" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1711" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1711" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1711" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1711" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1712" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1712" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1712" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1712" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1713" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1713" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1713" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1713" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1714" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1714" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1714" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1714" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1715" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1715" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1715" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1715" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1716" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1716" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1716" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1716" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1717" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1717" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1717" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1717" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1718" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1718" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1718" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1718" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1719" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1719" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1719" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1719" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1720" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1720" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1720" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1720" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1721" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1721" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1721" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1721" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1721"/>
+  <dimension ref="A1:F1738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45129,6 +45129,445 @@
         </is>
       </c>
     </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1722" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1722" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1722" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1722" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1723" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1723" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1723" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1723" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1724" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1724" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1724" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1724" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1725" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1725" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1725" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1725" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1726" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1726" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1726" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1727" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1727" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1727" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1727" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1728" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1728" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1728" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1728" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1729" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1729" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1729" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1729" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1730" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1730" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1730" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1730" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1731" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1731" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1731" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1731" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1732" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1732" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1732" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1732" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1733" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1733" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1733" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1733" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1734" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1734" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1734" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1734" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1735" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1735" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1735" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1735" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1736" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1736" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1736" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1736" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1737" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1737" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1737" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1738" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1738" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1738" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1738" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1738"/>
+  <dimension ref="A1:F1756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45568,6 +45568,471 @@
         </is>
       </c>
     </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1739" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1739" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1739" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1739" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>ACCHGS3Z9WNGWVPS</t>
+        </is>
+      </c>
+      <c r="B1740" t="n">
+        <v>140319905</v>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds NX Bluetooth (Pearl Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1740" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1740" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1740" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1741" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1741" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1741" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1741" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1742" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1742" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1742" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1743" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1743" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1743" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1743" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1744" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1744" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1744" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1745" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1745" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1745" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1745" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1746" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1746" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1746" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1746" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1747" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1747" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1747" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1747" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1748" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1748" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1748" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1749" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1749" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1749" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1750" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1750" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1750" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1751" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1751" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1751" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1752" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1752" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1752" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1752" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1753" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1753" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1753" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1753" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1754" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1754" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1754" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1754" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1755" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1755" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1755" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1755" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1756" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1756" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1756" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1756" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1756"/>
+  <dimension ref="A1:F1774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46033,6 +46033,471 @@
         </is>
       </c>
     </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1757" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1757" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1757" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>ACCHGS3Z9WNGWVPS</t>
+        </is>
+      </c>
+      <c r="B1758" t="n">
+        <v>140319905</v>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds NX Bluetooth (Pearl Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1758" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1758" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1758" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1759" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1759" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1759" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1759" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1760" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1760" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1760" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1761" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1761" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1761" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1761" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1762" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1762" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1762" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1763" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1763" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1763" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1763" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1764" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1764" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1764" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1764" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1765" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1765" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1765" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1765" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1766" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1766" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1766" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1766" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1767" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1767" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1767" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1767" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1768" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1768" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1768" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1768" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1769" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1769" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1769" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1769" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1770" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1770" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1770" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1770" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1771" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1771" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1771" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1771" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1772" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1772" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1772" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1772" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1773" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1773" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1773" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1773" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1774" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1774" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1774" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1774" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1774"/>
+  <dimension ref="A1:F1795"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46498,6 +46498,549 @@
         </is>
       </c>
     </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B1775" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D1775" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1775" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1775" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B1776" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1776" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1776" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1776" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B1777" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D1777" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1777" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1777" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1778" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1778" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1778" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1778" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>ACCHGS3Z9WNGWVPS</t>
+        </is>
+      </c>
+      <c r="B1779" t="n">
+        <v>140319905</v>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds NX Bluetooth (Pearl Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1779" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1779" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1779" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1780" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1780" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1780" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1780" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1781" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1781" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1781" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1781" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1782" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1782" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1782" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1782" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1783" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1783" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1783" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1784" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1784" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1784" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1784" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1785" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1785" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1785" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1785" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1786" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1786" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1786" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1786" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1787" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1787" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1787" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1787" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1788" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1788" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1788" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1788" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1789" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1789" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1789" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1789" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1790" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1790" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1790" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1790" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1791" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1791" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1791" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1791" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1792" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1792" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1792" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1792" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1793" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1793" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1793" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1793" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1794" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1794" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1794" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1794" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1795" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1795" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1795" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1795" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1795"/>
+  <dimension ref="A1:F1816"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47041,6 +47041,549 @@
         </is>
       </c>
     </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B1796" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D1796" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1796" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1796" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B1797" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1797" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1797" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1797" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B1798" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D1798" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1798" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1798" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1799" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1799" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1799" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1799" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>ACCHGS3Z9WNGWVPS</t>
+        </is>
+      </c>
+      <c r="B1800" t="n">
+        <v>140319905</v>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds NX Bluetooth (Pearl Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1800" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1800" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1800" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1801" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1801" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1801" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1801" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1802" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1802" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1802" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1802" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1803" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1803" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1803" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1803" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1804" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1804" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1804" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1805" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1805" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1805" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1805" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1806" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1806" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1806" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1806" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1807" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1807" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1807" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1807" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1808" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1808" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1808" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1808" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1809" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1809" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1809" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1809" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1810" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1810" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1810" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1810" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1811" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1811" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1811" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1811" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1812" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1812" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1812" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1812" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1813" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1813" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1813" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1813" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1814" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1814" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1814" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1814" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1815" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1815" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1815" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1815" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1816" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1816" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1816" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1816" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1816"/>
+  <dimension ref="A1:F1838"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47584,6 +47584,575 @@
         </is>
       </c>
     </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B1817" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D1817" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1817" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1817" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B1818" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1818" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1818" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1818" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B1819" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D1819" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1819" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1819" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1820" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1820" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1820" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1820" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>ACCHGS3Z9WNGWVPS</t>
+        </is>
+      </c>
+      <c r="B1821" t="n">
+        <v>140319905</v>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds NX Bluetooth (Pearl Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1821" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1821" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1821" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>ACCHGS3ZFPP57DKA</t>
+        </is>
+      </c>
+      <c r="B1822" t="n">
+        <v>140319903</v>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Turbo Bluetooth (Raven Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1822" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1822" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1822" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1823" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1823" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1823" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1823" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1824" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1824" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1824" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1824" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1825" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1825" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1825" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1825" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1826" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1826" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1826" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1827" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1827" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1827" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1827" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1828" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1828" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1828" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1828" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1829" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1829" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1829" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1829" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1830" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1830" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1830" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1830" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1831" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1831" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1831" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1831" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1832" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1832" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1832" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1832" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1833" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1833" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1833" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1833" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1834" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1834" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1834" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1834" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1835" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1835" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1835" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1835" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1836" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1836" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1836" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1836" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1837" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1837" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1837" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1838" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1838" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1838" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1838" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1838"/>
+  <dimension ref="A1:F1860"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48153,6 +48153,575 @@
         </is>
       </c>
     </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B1839" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D1839" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1839" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1839" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B1840" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1840" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1840" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B1841" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D1841" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1841" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1841" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1842" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1842" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1842" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>ACCHGS3Z9WNGWVPS</t>
+        </is>
+      </c>
+      <c r="B1843" t="n">
+        <v>140319905</v>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds NX Bluetooth (Pearl Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1843" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1843" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>ACCHGS3ZFPP57DKA</t>
+        </is>
+      </c>
+      <c r="B1844" t="n">
+        <v>140319903</v>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Turbo Bluetooth (Raven Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1844" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1844" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1844" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1845" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1845" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1845" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1845" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1846" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1846" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1846" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1846" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1847" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1847" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1847" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1847" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1848" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1848" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1848" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1849" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1849" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1849" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1849" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1850" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1850" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1850" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1850" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1851" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1851" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1851" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1851" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1852" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1852" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1852" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1852" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1853" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1853" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1853" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1853" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1854" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1854" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1854" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1854" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1855" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1855" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1855" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1855" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1856" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1856" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1856" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1856" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1857" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1857" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1857" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1857" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1858" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1858" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1858" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1858" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1859" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1859" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1859" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1859" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1860" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1860" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1860" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1860" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1860"/>
+  <dimension ref="A1:F1882"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48722,6 +48722,575 @@
         </is>
       </c>
     </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>ACCH8J5VFJQFSFSJ</t>
+        </is>
+      </c>
+      <c r="B1861" t="n">
+        <v>140319299</v>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones (Black)</t>
+        </is>
+      </c>
+      <c r="D1861" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1861" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1861" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>ACCHECD7TFHA8HMX</t>
+        </is>
+      </c>
+      <c r="B1862" t="n">
+        <v>140319790</v>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>PTron Studio Evo w/ 70Hrs Playtime,Dual Pairing,Pristine Audio,Clear Calls,Fast Charge Bluetooth Blue, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1862" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1862" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1862" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>ACCHECD7BFBHGVHK</t>
+        </is>
+      </c>
+      <c r="B1863" t="n">
+        <v>140319791</v>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>pTron Studio Evo Over-Ear BT Headphones with Mic (Beige)</t>
+        </is>
+      </c>
+      <c r="D1863" t="n">
+        <v>849</v>
+      </c>
+      <c r="E1863" t="n">
+        <v>699</v>
+      </c>
+      <c r="F1863" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1864" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1864" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1864" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1864" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>ACCHGS3Z9WNGWVPS</t>
+        </is>
+      </c>
+      <c r="B1865" t="n">
+        <v>140319905</v>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds NX Bluetooth (Pearl Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1865" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1865" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1865" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>ACCHGS3ZFPP57DKA</t>
+        </is>
+      </c>
+      <c r="B1866" t="n">
+        <v>140319903</v>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Turbo Bluetooth (Raven Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1866" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1866" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1866" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1867" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1867" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1867" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1867" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1868" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1868" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1868" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1868" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1869" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1869" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1869" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1869" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1870" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1870" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1870" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1871" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1871" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1871" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1871" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1872" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1872" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1872" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1872" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1873" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1873" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1873" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1873" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1874" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1874" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1874" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1874" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1875" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1875" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1875" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1875" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1876" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1876" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1876" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1876" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1877" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1877" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1877" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1877" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1878" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1878" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1878" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1878" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1879" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1879" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1879" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1879" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1880" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1880" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1880" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1880" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1881" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1881" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1881" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1881" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1882" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1882" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1882" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1882" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1882"/>
+  <dimension ref="A1:F1901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49291,6 +49291,497 @@
         </is>
       </c>
     </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1883" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1883" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1883" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1883" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>ACCHGS3Z9WNGWVPS</t>
+        </is>
+      </c>
+      <c r="B1884" t="n">
+        <v>140319905</v>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds NX Bluetooth (Pearl Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1884" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1884" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1884" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>ACCHGS3ZFPP57DKA</t>
+        </is>
+      </c>
+      <c r="B1885" t="n">
+        <v>140319903</v>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Turbo Bluetooth (Raven Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1885" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1885" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1885" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1886" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1886" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1886" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1886" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1887" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1887" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1887" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1887" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1888" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1888" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1888" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1888" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1889" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1889" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1889" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1890" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1890" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1890" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1890" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1891" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1891" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1891" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1891" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1892" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1892" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1892" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1892" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1893" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1893" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1893" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1893" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1894" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1894" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1894" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1894" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1895" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1895" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1895" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1895" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1896" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1896" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1896" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1896" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1897" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1897" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1897" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1897" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1898" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1898" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1898" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1898" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1899" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1899" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1899" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1899" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1900" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1900" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1900" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1900" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1901" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1901" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1901" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1901" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1901"/>
+  <dimension ref="A1:F1920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49782,6 +49782,497 @@
         </is>
       </c>
     </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1902" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1902" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1902" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1902" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>ACCHGS3Z9WNGWVPS</t>
+        </is>
+      </c>
+      <c r="B1903" t="n">
+        <v>140319905</v>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds NX Bluetooth (Pearl Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1903" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1903" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1903" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>ACCHGS3ZFPP57DKA</t>
+        </is>
+      </c>
+      <c r="B1904" t="n">
+        <v>140319903</v>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Turbo Bluetooth (Raven Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1904" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1904" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1904" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1905" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1905" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1905" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1905" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1906" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1906" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1906" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1906" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1907" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1907" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1907" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1907" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1908" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1908" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1908" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1909" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1909" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1909" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1909" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1910" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1910" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1910" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1910" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1911" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1911" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1911" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1911" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1912" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1912" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1912" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1912" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1913" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1913" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1913" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1913" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1914" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1914" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1914" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1914" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1915" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1915" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1915" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1915" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>ACCHJJVQ22DKYFH9</t>
+        </is>
+      </c>
+      <c r="B1916" t="n">
+        <v>140319898</v>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Beige, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1916" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1916" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F1916" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1917" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1917" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1917" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1917" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1918" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1918" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1918" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1918" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1919" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1919" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1919" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1919" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1920" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1920" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1920" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1920" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PA.xlsx
+++ b/PA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1920"/>
+  <dimension ref="A1:F1938"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50273,6 +50273,471 @@
         </is>
       </c>
     </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>ACCHZ33MPNUWHHG7</t>
+        </is>
+      </c>
+      <c r="B1921" t="n">
+        <v>140319732</v>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Spark Bluetooth Headset (Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1921" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1921" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1921" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>ACCHGS3Z9WNGWVPS</t>
+        </is>
+      </c>
+      <c r="B1922" t="n">
+        <v>140319905</v>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds NX Bluetooth (Pearl Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1922" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1922" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1922" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>ACCHGS3ZFPP57DKA</t>
+        </is>
+      </c>
+      <c r="B1923" t="n">
+        <v>140319903</v>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Turbo Bluetooth (Raven Black, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1923" t="n">
+        <v>749</v>
+      </c>
+      <c r="E1923" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1923" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>ACCHG53YY9FERTU8</t>
+        </is>
+      </c>
+      <c r="B1924" t="n">
+        <v>140319886</v>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Jet Black)</t>
+        </is>
+      </c>
+      <c r="D1924" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1924" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1924" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>ACCHHGUMAETTSGKE</t>
+        </is>
+      </c>
+      <c r="B1925" t="n">
+        <v>140319922</v>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>pTron Tangent Eon Wireless Neckband (Obsidian)</t>
+        </is>
+      </c>
+      <c r="D1925" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1925" t="n">
+        <v>569</v>
+      </c>
+      <c r="F1925" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>ACCGNPG4WH7MFD5Y</t>
+        </is>
+      </c>
+      <c r="B1926" t="n">
+        <v>140318112</v>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>pTron Bassstrings 4A with 18 Hrs Playtime,Deep Bass,Clear Calls &amp; Type C Fast Charging Bluetooth Headset  (Dark Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1926" t="n">
+        <v>469</v>
+      </c>
+      <c r="E1926" t="n">
+        <v>499</v>
+      </c>
+      <c r="F1926" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>ACCHH2KDUDPR5NEH</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>PTron Studio Ultima w/ 60hrs Playtime, Dual-Device Pairing, AI-ENC Calls,Custom EQ Bluetooth &amp; Wired Headset (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1927" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1927" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1927" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>ACCHG53YDGMAHC9G</t>
+        </is>
+      </c>
+      <c r="B1928" t="n">
+        <v>140319887</v>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (Blue)</t>
+        </is>
+      </c>
+      <c r="D1928" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1928" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1928" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>ACCHECD7VDTDFBZK</t>
+        </is>
+      </c>
+      <c r="B1929" t="n">
+        <v>140319773</v>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>PTron Bassbuds Fury w/ 50Hrs Playtime, Pristine Audio, Clear Calls, Bluetooth V5.4 Bluetooth Black, True Wireless</t>
+        </is>
+      </c>
+      <c r="D1929" t="n">
+        <v>568</v>
+      </c>
+      <c r="E1929" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1929" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>ACCHJJVQZYHXJTEZ</t>
+        </is>
+      </c>
+      <c r="B1930" t="n">
+        <v>140319897</v>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>pTron Studio Xtreme Bluetooth &amp; Wired (Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1930" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E1930" t="n">
+        <v>1149</v>
+      </c>
+      <c r="F1930" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>ACCHHB69UP5N4CDN</t>
+        </is>
+      </c>
+      <c r="B1931" t="n">
+        <v>140319876</v>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Blue, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1931" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1931" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1931" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>ACCHJJVQHM3XZPGJ</t>
+        </is>
+      </c>
+      <c r="B1932" t="n">
+        <v>140319896</v>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>pTron Studio Pixel Bluetooth &amp; Wired (Jet Black, On the Ear)</t>
+        </is>
+      </c>
+      <c r="D1932" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1932" t="n">
+        <v>999</v>
+      </c>
+      <c r="F1932" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>ACCHMH9QBUGKZNV5</t>
+        </is>
+      </c>
+      <c r="B1933" t="n">
+        <v>140319982</v>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Indie TWS Earbuds (White)</t>
+        </is>
+      </c>
+      <c r="D1933" t="n">
+        <v>549</v>
+      </c>
+      <c r="E1933" t="n">
+        <v>599</v>
+      </c>
+      <c r="F1933" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>ACCHMH9QSGHAZGDA</t>
+        </is>
+      </c>
+      <c r="B1934" t="n">
+        <v>140319984</v>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Verse OWS Earbuds (Pearl Purple)</t>
+        </is>
+      </c>
+      <c r="D1934" t="n">
+        <v>826.6485</v>
+      </c>
+      <c r="E1934" t="n">
+        <v>899</v>
+      </c>
+      <c r="F1934" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>ACCHEPDX3Z9FKZBG</t>
+        </is>
+      </c>
+      <c r="B1935" t="n">
+        <v>140320000</v>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>PTron Studio Sports Bluetooth Gaming Black, On the Ear</t>
+        </is>
+      </c>
+      <c r="D1935" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E1935" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F1935" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>ACCH6WEZB5CMVEMJ</t>
+        </is>
+      </c>
+      <c r="B1936" t="n">
+        <v>140319615</v>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>pTron Basspods Tour with AI-ENC Calls, 45hrs Playback, Pristine Audio,50ms Low Latency Bluetooth  (Blue, True Wireless)</t>
+        </is>
+      </c>
+      <c r="D1936" t="n">
+        <v>499</v>
+      </c>
+      <c r="E1936" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1936" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>ACCHHB69USVX6ZBY</t>
+        </is>
+      </c>
+      <c r="B1937" t="n">
+        <v>140319877</v>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Eon Bluetooth  (Grey, In the Ear)</t>
+        </is>
+      </c>
+      <c r="D1937" t="n">
+        <v>598</v>
+      </c>
+      <c r="E1937" t="n">
+        <v>649</v>
+      </c>
+      <c r="F1937" t="inlineStr">
+        <is>
+          <t>Current price is More than Amazon price</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>ACCGNFUYZWFJPHH8</t>
+        </is>
+      </c>
+      <c r="B1938" t="n">
+        <v>140318654</v>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>pTron Bassbuds Joy TWS with 13mm Drivers, Stereo Calls, 32Hrs Playtime,Type-C Charging (Black)</t>
+        </is>
+      </c>
+      <c r="D1938" t="n">
+        <v>599</v>
+      </c>
+      <c r="E1938" t="n">
+        <v>399</v>
+      </c>
+      <c r="F1938" t="inlineStr">
+        <is>
+          <t>Current price is Less than Amazon price</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
